--- a/ucd.xlsx
+++ b/ucd.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,139 +11,172 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
   <si>
     <t>WS</t>
   </si>
   <si>
+    <t>Jamie Yip</t>
+  </si>
+  <si>
+    <t>Carolyn Suryapermana</t>
+  </si>
+  <si>
+    <t>Chonticha Phanphanit</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>Leyang Ding</t>
+  </si>
+  <si>
+    <t>Richard Huang</t>
+  </si>
+  <si>
+    <t>Benson Ngai</t>
+  </si>
+  <si>
+    <t>Geoffray Lee</t>
+  </si>
+  <si>
+    <t>Jon Moser</t>
+  </si>
+  <si>
+    <t>Jonathan Li</t>
+  </si>
+  <si>
+    <t>Sidney Wang</t>
+  </si>
+  <si>
+    <t>Adrian Luo</t>
+  </si>
+  <si>
+    <t>Mariano Elizondo</t>
+  </si>
+  <si>
+    <t>Jerry Qiu</t>
+  </si>
+  <si>
+    <t>Sean Tan</t>
+  </si>
+  <si>
+    <t>Kevin Cuan</t>
+  </si>
+  <si>
+    <t>Aaron Lim</t>
+  </si>
+  <si>
+    <t>Bill Wong</t>
+  </si>
+  <si>
+    <t>Daniel Lin</t>
+  </si>
+  <si>
+    <t>Yawei He</t>
+  </si>
+  <si>
+    <t>Jordon Kwong</t>
+  </si>
+  <si>
+    <t>Chimnay</t>
+  </si>
+  <si>
+    <t>Michael Salim</t>
+  </si>
+  <si>
+    <t>Kyle Kimura</t>
+  </si>
+  <si>
+    <t>Ryan Lei</t>
+  </si>
+  <si>
+    <t>Adrian Luu</t>
+  </si>
+  <si>
+    <t>Josh Luo</t>
+  </si>
+  <si>
+    <t>Karthik Villavan</t>
+  </si>
+  <si>
+    <t>Marc Ethan Saguiped</t>
+  </si>
+  <si>
+    <t>Donnovan Saelee</t>
+  </si>
+  <si>
+    <t>WD</t>
+  </si>
+  <si>
+    <t>Xin Huang</t>
+  </si>
+  <si>
+    <t>Betty Yang</t>
+  </si>
+  <si>
+    <t>Kristine Ngo</t>
+  </si>
+  <si>
     <t>Erika Lai</t>
   </si>
   <si>
-    <t>Joy Yang</t>
-  </si>
-  <si>
-    <t>Kristine Ngo</t>
-  </si>
-  <si>
-    <t>Elaine Tsou</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>Richard Huang</t>
-  </si>
-  <si>
-    <t>Jun Jie Lai</t>
-  </si>
-  <si>
-    <t>Leyang Ding</t>
-  </si>
-  <si>
-    <t>Robert Chang</t>
-  </si>
-  <si>
-    <t>Jon Moser</t>
-  </si>
-  <si>
-    <t>Kyle Fang</t>
-  </si>
-  <si>
-    <t>Vo Ly</t>
-  </si>
-  <si>
-    <t>Brandon Leung</t>
-  </si>
-  <si>
-    <t>Justin Larson</t>
-  </si>
-  <si>
-    <t>Samarth Sridhara</t>
-  </si>
-  <si>
-    <t>Jonathan Li</t>
-  </si>
-  <si>
-    <t>Sean Tan</t>
-  </si>
-  <si>
-    <t>Bill Wong</t>
-  </si>
-  <si>
-    <t>Donald Ly</t>
-  </si>
-  <si>
-    <t>Andy Li</t>
-  </si>
-  <si>
-    <t>Jason Wu</t>
-  </si>
-  <si>
-    <t>Junru Su</t>
-  </si>
-  <si>
-    <t>Aaron Lim</t>
-  </si>
-  <si>
-    <t>Neil Patel</t>
-  </si>
-  <si>
-    <t>Andrew Yeow</t>
-  </si>
-  <si>
-    <t>WD</t>
-  </si>
-  <si>
-    <t>Xin Huang</t>
-  </si>
-  <si>
-    <t>Claudia Xu</t>
-  </si>
-  <si>
-    <t>Aditi Kavipurapu</t>
-  </si>
-  <si>
     <t>Muyen Liang</t>
   </si>
   <si>
-    <t>Julie La</t>
-  </si>
-  <si>
-    <t>Khanh Tran</t>
+    <t>Livia Rice</t>
+  </si>
+  <si>
+    <t>Isabella Li</t>
+  </si>
+  <si>
+    <t>Winnie Wu</t>
+  </si>
+  <si>
+    <t>Mallika Chou</t>
   </si>
   <si>
     <t>MS</t>
   </si>
   <si>
+    <t>Adrian Li</t>
+  </si>
+  <si>
+    <t>Finn</t>
+  </si>
+  <si>
+    <t>Booker Brown</t>
+  </si>
+  <si>
     <t>XD</t>
   </si>
   <si>
-    <t>Richard huang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Chang </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew Yeow </t>
-  </si>
-  <si>
-    <t>Ken Sibal</t>
-  </si>
-  <si>
-    <t>Muyen</t>
-  </si>
-  <si>
-    <t>Adrian Luo</t>
-  </si>
-  <si>
-    <t>Julie Ma</t>
+    <t>Iris Lee</t>
+  </si>
+  <si>
+    <t>Adam Dinh</t>
+  </si>
+  <si>
+    <t>Minh Nguyen</t>
+  </si>
+  <si>
+    <t>Ehong Ng</t>
+  </si>
+  <si>
+    <t>Gaby Solei</t>
+  </si>
+  <si>
+    <t>Carolyn Surypermana</t>
+  </si>
+  <si>
+    <t>Suhani Shokeen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -151,29 +184,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -196,30 +213,24 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -231,6 +242,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -465,406 +480,555 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4" t="s">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4" t="s">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="4" t="s">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>13</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="4" t="s">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>15</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="4" t="s">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="5" t="s">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>19</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="5" t="s">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="5" t="s">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>23</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="5" t="s">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>25</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>23</v>
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="A19" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
-      <c r="B20" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
     </row>
     <row r="21">
-      <c r="A21" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>27</v>
+      <c r="A21" s="1"/>
+      <c r="B21" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>1</v>
+        <v>1.0</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>30</v>
+        <v>2.0</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>32</v>
+        <v>3.0</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>1</v>
+        <v>4.0</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>30</v>
+        <v>5.0</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
-      <c r="B28" s="7" t="s">
-        <v>33</v>
+      <c r="B28" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2">
         <v>1.0</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>7</v>
+      <c r="B29" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2">
         <v>2.0</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>8</v>
+      <c r="B30" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2">
         <v>3.0</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>9</v>
+      <c r="B31" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2">
         <v>4.0</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>24</v>
+      <c r="B32" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2">
         <v>5.0</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>25</v>
+      <c r="B33" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2">
         <v>6.0</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>11</v>
+      <c r="B34" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2">
         <v>7.0</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-    </row>
     <row r="37">
-      <c r="A37" s="1"/>
-      <c r="B37" s="2" t="s">
-        <v>34</v>
+      <c r="A37" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="1"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1"/>
+      <c r="B46" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
         <v>7.0</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2">
+      <c r="B53" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
         <v>8.0</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>41</v>
+      <c r="B54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="24">
+    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
